--- a/Test/TestResult_5_5_3_4_3_1_CRP_2Stage_ALNS_5_RQMC_42_Q_S_1_0_AE_NoC_Re-solve_10_1_0.xlsx
+++ b/Test/TestResult_5_5_3_4_3_1_CRP_2Stage_ALNS_5_RQMC_42_Q_S_1_0_AE_NoC_Re-solve_10_1_0.xlsx
@@ -747,7 +747,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8114245.06</v>
+        <v>8114245.09</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>1418</v>
       </c>
       <c r="L2" t="n">
-        <v>14587.22791295683</v>
+        <v>14587.22791295681</v>
       </c>
       <c r="M2" t="n">
         <v>5239550.388066329</v>
@@ -813,7 +813,7 @@
         <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="X2" t="n">
         <v>2</v>
@@ -995,13 +995,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8288464.664243907</v>
+        <v>8288464.694243906</v>
       </c>
       <c r="B2" t="n">
-        <v>1978741.987412721</v>
+        <v>1978742.017412721</v>
       </c>
       <c r="C2" t="n">
-        <v>14598187.34107509</v>
+        <v>14598187.37107509</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1013,10 +1013,10 @@
         <v>-1</v>
       </c>
       <c r="G2" t="n">
-        <v>19030.91220849908</v>
+        <v>19030.94220849909</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>3</v>
       </c>
       <c r="AC2" t="n">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="AD2" t="n">
         <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.186441659927368</v>
+        <v>4.453642606735229</v>
       </c>
     </row>
   </sheetData>
